--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA137"/>
+  <dimension ref="A1:AA140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15217,6 +15217,297 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>The Barrel Thailand</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>The Barrel Thailand</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>103819</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>809 Soi Phatthanakan 30</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://thebarrel.asia</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>thebarrelthai@thebarrel.asia</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 136 8500</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="R138" s="2" t="inlineStr"/>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thebarrelthailand/</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thebarrelthailand</t>
+        </is>
+      </c>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr"/>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>41594</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>No.8 Rama 9 Soi 43 (soi 17 Seri 4), Rama 9 Road</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sibour.com</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>md@sibour.com</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 300 5613</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>0105540066099</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comte-de-sibour/</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sibourlimited</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>Claude Lapeyre</t>
+        </is>
+      </c>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>Sales Supervisor</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/claude-lapeyre-52598658/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>41594</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>No.8 Rama 9 Soi 43 (soi 17 Seri 4), Rama 9 Road</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sibour.com</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>md@sibour.com</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 300 5613</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0105540066099</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comte-de-sibour/</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sibourlimited</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>Christophe Imbert</t>
+        </is>
+      </c>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christophe-imbert-49804875/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA140"/>
+  <dimension ref="A1:AA169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15508,6 +15508,2239 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Lovely Wines</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr"/>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>168901</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>28 Krungthep Kritha 27 Alley, Lane 2, Thap Chang, Saphan Sung</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>https://lovelywines.co.th</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Info@lovelywines.co.th</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 318 1588</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr"/>
+      <c r="R141" s="2" t="inlineStr"/>
+      <c r="S141" s="2" t="inlineStr"/>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr"/>
+      <c r="X141" s="2" t="inlineStr"/>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GFour Food and Beverage</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>168900</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>20, 22 Right Side, Soi Chan 43 Yaek 45, Bangklo Bangkolam</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>10120</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gfour.co.th</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>sales@gfour.co.th</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 674 0836</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr"/>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gfourtaste</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gfourtaste</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gfourtaste/</t>
+        </is>
+      </c>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>Aronne Gregorini</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aronne-gregorini-a3b5431a1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>GFour Food and Beverage</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr"/>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>168900</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>20, 22 Right Side, Soi Chan 43 Yaek 45, Bangklo Bangkolam</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>10120</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gfour.co.th</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>sales@gfour.co.th</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 674 0836</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr"/>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gfourtaste</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gfourtaste</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gfourtaste/</t>
+        </is>
+      </c>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>Luca Bernardinetti</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luca-bernardinetti-750b9654/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>GFour Food and Beverage</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>168900</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>20, 22 Right Side, Soi Chan 43 Yaek 45, Bangklo Bangkolam</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>10120</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gfour.co.th</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>sales@gfour.co.th</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 674 0836</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr"/>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gfourtaste</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gfourtaste</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gfourtaste/</t>
+        </is>
+      </c>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>Anchalee Polsunsri</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anchalee-polsunsri-685947239/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>German Dragon Co Ltd</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr"/>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>168899</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Banglamung</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Chonburi</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>359/16 Moo 7, Nong Prue</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>20150</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>https://germandragon.com</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>info@germandragon.com</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr"/>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr"/>
+      <c r="R145" s="2" t="inlineStr"/>
+      <c r="S145" s="2" t="inlineStr"/>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
+      <c r="X145" s="2" t="inlineStr"/>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Fantastico Company Limited</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr"/>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>168898</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Krathum Baen</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Samut Sakhon</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>29/3 Thanon Leabklongkhaerai, Suan Luang</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>74110</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://fantastico.co.th/about-us</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>fantasticothailand@gmail.com</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>+66 34 112 289</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr"/>
+      <c r="R146" s="2" t="inlineStr"/>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fantasticowine</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fantasticowine/</t>
+        </is>
+      </c>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr"/>
+      <c r="X146" s="2" t="inlineStr"/>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Savio Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr"/>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>168897</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>09/11 Phuttamonthon Sai 2 Soi 23, Sala Thammasop, Thawi Watthana</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>10170</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.savioco.com</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>info@savioco.com</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr"/>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr"/>
+      <c r="R147" s="2" t="inlineStr"/>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/saviothailand</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/savio.thailand/</t>
+        </is>
+      </c>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr"/>
+      <c r="X147" s="2" t="inlineStr"/>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>TA Beverage Distribution Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr"/>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>168896</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Thanyaburi</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Pathum Thani</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>94 Paholyothin Rd. Prachathipat</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ta-beverage.com</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>tabev.d@gmail.com</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 101 9988</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="R148" s="2" t="inlineStr"/>
+      <c r="S148" s="2" t="inlineStr"/>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr"/>
+      <c r="X148" s="2" t="inlineStr"/>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Double A Distribution Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr"/>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>168894</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>548 One City Centre, 37th Floors, Ploenchit Road, Lumpini, Pathumwan</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>10330</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://aa-distribution.com</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>sales@aa-distribution.com</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr"/>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr"/>
+      <c r="R149" s="2" t="inlineStr"/>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DADdoublea</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr"/>
+      <c r="X149" s="2" t="inlineStr"/>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Wine Aspect Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr"/>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>168893</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>113/6 Thong Lor</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://wineaspectbkk.com</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>info.wineaspect@gmail.com</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr"/>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineaspectbkk/</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr"/>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine_aspect/</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>Iris van Moorsel</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>Brand Ambassador</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/iris-van-moorsel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Wine Aspect Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr"/>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>168893</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>113/6 Thong Lor</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://wineaspectbkk.com</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>info.wineaspect@gmail.com</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr"/>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr"/>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineaspectbkk/</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr"/>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine_aspect/</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>Rapheephan Bew Naweera</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rapheephan-bew-naweera-146124256/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>MK Import and Supply Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr"/>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>168892</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>19/9 M9 Building, Soi Phueng Mi 1, Sukhumvit Road</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>10260</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://mkiands.co.th</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>contact@mkiands.co.th</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr"/>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="R152" s="2" t="inlineStr"/>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594058521575</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr"/>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Globo Vista IT Company Limited</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr"/>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>168891</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>99/9 Phahonyothin 30</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://globovista.com</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>will@globovista.com</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr"/>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr"/>
+      <c r="R153" s="2" t="inlineStr"/>
+      <c r="S153" s="2" t="inlineStr"/>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
+      <c r="X153" s="2" t="inlineStr"/>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Milano Bangkok Consulting Co., Ltd. </t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Ithai Wine Division</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>168890</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>20Fl, United Business Center II, Sukhumvit Rd, Klongton, Watthana</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://ithai.wine</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>info@ithai.eu</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>+39 02 5412 2724</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr"/>
+      <c r="R154" s="2" t="inlineStr"/>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61565559652429</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ithaiwinedivision</t>
+        </is>
+      </c>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
+      <c r="X154" s="2" t="inlineStr"/>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>The Best Provider Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr"/>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>168889</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>559/18 Soi Pattanakarn 32, Suanluang, Suanluang</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thebestproviders.com</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>info.thebestprovider@gmail.com</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr"/>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr"/>
+      <c r="R155" s="2" t="inlineStr"/>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheBestProviderr</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thebest.provider/</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr"/>
+      <c r="X155" s="2" t="inlineStr"/>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Oriental Vinesories</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr"/>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>168887</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Shropshire</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>26 Wyle Cop</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>SY1 1XD</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.orientalvinesories.com</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>info@orientalvinesories.com</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr"/>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr"/>
+      <c r="R156" s="2" t="inlineStr"/>
+      <c r="S156" s="2" t="inlineStr"/>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>Kritidech (Krit) Srabua</t>
+        </is>
+      </c>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Oriental Vinesories</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr"/>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>168887</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Shropshire</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>26 Wyle Cop</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>SY1 1XD</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.orientalvinesories.com</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>info@orientalvinesories.com</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr"/>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr"/>
+      <c r="R157" s="2" t="inlineStr"/>
+      <c r="S157" s="2" t="inlineStr"/>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>Thanat (Tee) Srabua</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Importing</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Roughrhino Beverage Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr"/>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>168886</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Phra Pradaeng</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Samut Prakan</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>13/39, Moo 13</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://theroughrhino.com</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>roughrhinobev@gmail.com</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="inlineStr"/>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/369800889862762</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr"/>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Pookan International Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr"/>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>168864</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Kathu</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>159/6-7, Nanai, Pa Tong</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://pookan.net</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>info@pookan.net</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr"/>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr"/>
+      <c r="R159" s="2" t="inlineStr"/>
+      <c r="S159" s="2" t="inlineStr"/>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr"/>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Wine Lamo Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr"/>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>168862</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>1-5-5 501, Mita, Minato</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://winelamo.com</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>th@winelamo.com</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 625 3019</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr"/>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winelamo/</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61559635313324&amp;mibextid=LQQJ4d</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winelamo_thailand/</t>
+        </is>
+      </c>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>Tomomitsu Mori</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomomitsu-mori-b197527b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Wine Lamo Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr"/>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>168862</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>1-5-5 501, Mita, Minato</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://winelamo.com</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>th@winelamo.com</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 625 3019</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr"/>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winelamo/</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61559635313324&amp;mibextid=LQQJ4d</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winelamo_thailand/</t>
+        </is>
+      </c>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>Bupakorn Sricheewachart</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/bupakorn-sricheewachart</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Little Gourmande Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>168861</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>33/4 The Ninth Tower Grand Rama 9, Rama 9 Road, 35th Floor, Huaykwang, Huaykwang</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>10310</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.littlegourmande.com</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>hello@littlegourmande.com</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr"/>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="R162" s="2" t="inlineStr"/>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61578390290301&amp;mibextid=wwXIfr&amp;rdid=w1rKziJFvfgaT1at&amp;share_url=https%3A%2F%2Fwww.facebook.com%2Fshare%2F1ALToqrMBF%2F%3Fmibextid%3DwwXIfr</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littlegourmande.official/</t>
+        </is>
+      </c>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr"/>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Jindi Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr"/>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>168860</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Bang Kruai District</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Nonthaburi</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>62/2 Moo 7, Soi Bang Kruai-Sai Noi 13/3, Bang Kruai-Sai Noi Road</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>11130</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jindi.co.th</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>watcharee@jindi.co.th</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr"/>
+      <c r="P163" s="2" t="inlineStr"/>
+      <c r="Q163" s="2" t="inlineStr"/>
+      <c r="R163" s="2" t="inlineStr"/>
+      <c r="S163" s="2" t="inlineStr"/>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr"/>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Wijnhoos Wine Company</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr"/>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>168859</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>9/106 Soi Lat Krabang 1Kor/14, Lat Krabang Road, Lat Krabang</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>10520</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wijnhoos.com</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>admin@wijnhoos.com</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr"/>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="R164" s="2" t="inlineStr"/>
+      <c r="S164" s="2" t="inlineStr"/>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr"/>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Glt Italia Company Limited</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Glt Italia Company Limited</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>111021</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Tambon Bang Rak Noi</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Chang Wat Nonthaburi, Amphoe Mueang Nonthaburi</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>103/17 Thanon Ratchaphruek</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glt-italia.com</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>glt.wine.sale@gmail.com</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 118 6377</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr"/>
+      <c r="R165" s="2" t="inlineStr"/>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/glt.italianwine</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gltitalia/</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Baiano</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antoniobaiano/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Wine Dee Dee Company Limited</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Wine Dee Dee Company Limited</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>122567</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Tambon Bang Talat</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Chang Wat Nonthaburi, Amphoe Pak Kret</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>8 Thanon Pracha Chuen</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>11120</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winedeedeegroup.com</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>wdd@winedeedee.com</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 984 4845</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0205543004051</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr"/>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr"/>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>The Barrel Thailand</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>The Barrel Thailand</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>103819</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>809 Soi Phatthanakan 30</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://thebarrel.asia</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>thebarrelthai@thebarrel.asia</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 136 8500</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr"/>
+      <c r="R167" s="2" t="inlineStr"/>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thebarrelthailand/</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thebarrelthailand</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr"/>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>41594</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>No.8 Rama 9 Soi 43 (soi 17 Seri 4), Rama 9 Road</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sibour.com</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>md@sibour.com</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 300 5613</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0105540066099</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comte-de-sibour/</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sibourlimited</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>Claude Lapeyre</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>Sales Supervisor</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/claude-lapeyre-52598658/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>41594</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>No.8 Rama 9 Soi 43 (soi 17 Seri 4), Rama 9 Road</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sibour.com</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>md@sibour.com</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 300 5613</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>0105540066099</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comte-de-sibour/</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sibourlimited</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>Christophe Imbert</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christophe-imbert-49804875/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA169"/>
+  <dimension ref="A1:AA174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17741,6 +17741,475 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Glt Italia Company Limited</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Glt Italia Company Limited</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>111021</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Tambon Bang Rak Noi</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Chang Wat Nonthaburi, Amphoe Mueang Nonthaburi</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>103/17 Thanon Ratchaphruek</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glt-italia.com</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>glt.wine.sale@gmail.com</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 118 6377</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr"/>
+      <c r="R170" s="2" t="inlineStr"/>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/glt.italianwine</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gltitalia/</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Baiano</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antoniobaiano/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Wine Dee Dee Company Limited</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Wine Dee Dee Company Limited</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>122567</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Tambon Bang Talat</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Chang Wat Nonthaburi, Amphoe Pak Kret</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>8 Thanon Pracha Chuen</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>11120</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winedeedeegroup.com</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>wdd@winedeedee.com</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 984 4845</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>0205543004051</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr"/>
+      <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr"/>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>The Barrel Thailand</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>The Barrel Thailand</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>103819</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>809 Soi Phatthanakan 30</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://thebarrel.asia</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>thebarrelthai@thebarrel.asia</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 136 8500</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr"/>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thebarrelthailand/</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thebarrelthailand</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr"/>
+      <c r="X172" s="2" t="inlineStr"/>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>41594</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>No.8 Rama 9 Soi 43 (soi 17 Seri 4), Rama 9 Road</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sibour.com</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>md@sibour.com</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 300 5613</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0105540066099</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comte-de-sibour/</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sibourlimited</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>Claude Lapeyre</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>Sales Supervisor</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/claude-lapeyre-52598658/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Comte De Sibour Limited</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>41594</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Khet Suan Luang</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>No.8 Rama 9 Soi 43 (soi 17 Seri 4), Rama 9 Road</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sibour.com</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>md@sibour.com</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 300 5613</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>0105540066099</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/comte-de-sibour/</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sibourlimited</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>Christophe Imbert</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christophe-imbert-49804875/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
